--- a/data/assumptions.xlsx
+++ b/data/assumptions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ekosltd-my.sharepoint.com/personal/alessia_biris_ekos_co_uk/Documents/TCL/code_dashboard/v2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="8_{FA218BAD-3EBA-47B7-9DEF-468792D266E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B13E0E0-1B93-4B0D-BF9F-A584971B8A78}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{FA218BAD-3EBA-47B7-9DEF-468792D266E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FA303A8-BBEE-4BD1-8454-7FFFA21B5672}"/>
   <bookViews>
-    <workbookView xWindow="7065" yWindow="-14250" windowWidth="19725" windowHeight="14415" firstSheet="7" activeTab="10" xr2:uid="{5C67809F-44A3-4AFA-BBD2-6581972C325D}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="13" xr2:uid="{5C67809F-44A3-4AFA-BBD2-6581972C325D}"/>
   </bookViews>
   <sheets>
     <sheet name="general_parameters" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="192">
   <si>
     <t>Parameter</t>
   </si>
@@ -614,6 +614,21 @@
   </si>
   <si>
     <t>Land value default for leakage</t>
+  </si>
+  <si>
+    <t>Older person</t>
+  </si>
+  <si>
+    <t>Heritage asset LS</t>
+  </si>
+  <si>
+    <t>Annual revenue saving per unit for public sector infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">£ / unit </t>
+  </si>
+  <si>
+    <t>New annual revenue stream, needs NPV discounting</t>
   </si>
 </sst>
 </file>
@@ -658,7 +673,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,6 +688,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -840,7 +861,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -1018,11 +1039,17 @@
     <xf numFmtId="171" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="150">
+  <dxfs count="151">
     <dxf>
       <font>
         <b val="0"/>
@@ -1999,6 +2026,321 @@
         </right>
         <top/>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2030,7 +2372,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2039,6 +2383,326 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="168" formatCode="0.00%;[Red]\(0.00%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2070,9 +2734,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2179,12 +2841,103 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -2356,6 +3109,1147 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="167" formatCode="0.0000"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2387,9 +4281,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2496,6 +4388,174 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Avenir Next LT Pro"/>
         <family val="2"/>
@@ -2638,6 +4698,139 @@
         </bottom>
         <vertical/>
         <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -2669,9 +4862,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -2680,326 +4871,6 @@
         </bottom>
         <vertical/>
         <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="168" formatCode="0.00%;[Red]\(0.00%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
     <dxf>
@@ -3031,7 +4902,9 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -3138,12 +5011,102 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color rgb="FF666666"/>
         <name val="Avenir Next LT Pro"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -3151,1902 +5114,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="167" formatCode="0.0000"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="165" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -5108,42 +5175,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}" name="general_parameters" displayName="general_parameters" ref="A1:D8" totalsRowShown="0" headerRowDxfId="149" headerRowBorderDxfId="148" tableBorderDxfId="147" totalsRowBorderDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}" name="general_parameters" displayName="general_parameters" ref="A1:D8" totalsRowShown="0" headerRowDxfId="139" headerRowBorderDxfId="138" tableBorderDxfId="137" totalsRowBorderDxfId="136">
   <autoFilter ref="A1:D8" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BF4A73EA-A313-4283-BE5C-5B9F6C2039F3}" name="Parameter" dataDxfId="145"/>
+    <tableColumn id="1" xr3:uid="{BF4A73EA-A313-4283-BE5C-5B9F6C2039F3}" name="Parameter" dataDxfId="135"/>
     <tableColumn id="2" xr3:uid="{2168A1D6-1F00-420A-AE49-628879EF67CF}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{EE2AD78A-DCFF-47D8-A4FD-47301D7A564F}" name="Units" dataDxfId="144"/>
-    <tableColumn id="4" xr3:uid="{F7910500-F089-4E59-9AC8-5734EF06B071}" name="Source / note" dataDxfId="143"/>
+    <tableColumn id="3" xr3:uid="{EE2AD78A-DCFF-47D8-A4FD-47301D7A564F}" name="Units" dataDxfId="134"/>
+    <tableColumn id="4" xr3:uid="{F7910500-F089-4E59-9AC8-5734EF06B071}" name="Source / note" dataDxfId="133"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}" name="household_spend" displayName="household_spend" ref="A1:E11" totalsRowShown="0" headerRowDxfId="63" dataDxfId="61" headerRowBorderDxfId="62" tableBorderDxfId="60" totalsRowBorderDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}" name="household_spend" displayName="household_spend" ref="A1:E11" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
   <autoFilter ref="A1:E11" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9A4690EE-FA56-405E-A30D-875570657134}" name="Typology / tenure" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{E91F277E-06CE-4EDB-8543-29E44E82DEA7}" name="Upper" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{1EAAF470-471D-4B0C-A575-DFBD58AEA1B8}" name="Central" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{57C7CBC2-465E-4D9C-862C-8B255FF6A5B2}" name="Lower" dataDxfId="55"/>
-    <tableColumn id="5" xr3:uid="{2AC2BF98-5348-4DE0-93F2-91C9D65F223E}" name="Units" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{9A4690EE-FA56-405E-A30D-875570657134}" name="Typology / tenure" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{E91F277E-06CE-4EDB-8543-29E44E82DEA7}" name="Upper" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{1EAAF470-471D-4B0C-A575-DFBD58AEA1B8}" name="Central" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{57C7CBC2-465E-4D9C-862C-8B255FF6A5B2}" name="Lower" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{2AC2BF98-5348-4DE0-93F2-91C9D65F223E}" name="Units" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}" name="additionality_mappings" displayName="additionality_mappings" ref="A1:F16" totalsRowShown="0" headerRowDxfId="53" dataDxfId="51" headerRowBorderDxfId="52" tableBorderDxfId="50" totalsRowBorderDxfId="49">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}" name="additionality_mappings" displayName="additionality_mappings" ref="A1:F16" totalsRowShown="0" headerRowDxfId="150" dataDxfId="148" headerRowBorderDxfId="149" tableBorderDxfId="147" totalsRowBorderDxfId="146">
   <autoFilter ref="A1:F16" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E3A723FA-457B-4EFE-9E92-EB013E337B59}" name="Group" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{02D51F27-6686-45C8-B830-EE4683B203DE}" name="Scenario" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{141761B2-F5F5-4B9A-8B3E-DC8AC7A74CBC}" name="Deadweight" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{73079F49-39D1-41A2-AF81-9562C0ADE495}" name="Displacement" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{BF1D37EB-AE48-4C08-9998-896BCDE53C45}" name="Leakage" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{343EC36C-1426-4634-AD97-7726BDCCA977}" name="Multiplier" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{E3A723FA-457B-4EFE-9E92-EB013E337B59}" name="Group" dataDxfId="145"/>
+    <tableColumn id="2" xr3:uid="{02D51F27-6686-45C8-B830-EE4683B203DE}" name="Scenario" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{141761B2-F5F5-4B9A-8B3E-DC8AC7A74CBC}" name="Deadweight" dataDxfId="143"/>
+    <tableColumn id="4" xr3:uid="{73079F49-39D1-41A2-AF81-9562C0ADE495}" name="Displacement" dataDxfId="142"/>
+    <tableColumn id="5" xr3:uid="{BF1D37EB-AE48-4C08-9998-896BCDE53C45}" name="Leakage" dataDxfId="141"/>
+    <tableColumn id="6" xr3:uid="{343EC36C-1426-4634-AD97-7726BDCCA977}" name="Multiplier" dataDxfId="140"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5176,8 +5243,8 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}" name="land_infra_mult" displayName="land_infra_mult" ref="A1:D8" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
-  <autoFilter ref="A1:D8" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}" name="land_infra_mult" displayName="land_infra_mult" ref="A1:D9" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+  <autoFilter ref="A1:D9" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{7FD0A6E6-1B0A-4FC7-81EC-4DD560B478DC}" name="Parameter" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{A7B1CC4E-78DF-4D14-A750-3E88F52FAF2A}" name="Value"/>
@@ -5237,117 +5304,118 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}" name="dwellingbytypology" displayName="dwellingbytypology" ref="A1:H6" totalsRowShown="0" headerRowDxfId="142" dataDxfId="140" headerRowBorderDxfId="141" tableBorderDxfId="139" totalsRowBorderDxfId="138">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}" name="dwellingbytypology" displayName="dwellingbytypology" ref="A1:H6" totalsRowShown="0" headerRowDxfId="132" dataDxfId="130" headerRowBorderDxfId="131" tableBorderDxfId="129" totalsRowBorderDxfId="128">
   <autoFilter ref="A1:H6" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AF5B1002-ACF0-443F-BA91-D855456C8E2D}" name="Typology" dataDxfId="137"/>
-    <tableColumn id="2" xr3:uid="{4552E384-A064-4D7E-B638-6DC25252B385}" name="Floorspace m2" dataDxfId="136"/>
-    <tableColumn id="3" xr3:uid="{E22864B2-160F-4F3D-9491-0A60A9310C41}" name="Persons Per Dwelling - Private" dataDxfId="135"/>
-    <tableColumn id="4" xr3:uid="{0377E05F-6D73-4E82-AD3D-2AA209958578}" name="Persons Per Dwelling - Social/affordable" dataDxfId="134"/>
-    <tableColumn id="5" xr3:uid="{3D93BA7B-360E-4A20-BB94-AFEC8DAB2F05}" name="Council Tax per unit" dataDxfId="133"/>
-    <tableColumn id="6" xr3:uid="{E1042461-7B4B-4E4A-96C1-EA75409C533A}" name="Rent per social/MMR unit" dataDxfId="132"/>
-    <tableColumn id="7" xr3:uid="{56B6CFB9-570D-4CC0-9162-B0D0FCE94F69}" name="Private disposable income" dataDxfId="131"/>
-    <tableColumn id="8" xr3:uid="{CA5B102B-23EE-4F5D-853D-87DFD7D74ACA}" name="Social/affordable disposable income" dataDxfId="130"/>
+    <tableColumn id="1" xr3:uid="{AF5B1002-ACF0-443F-BA91-D855456C8E2D}" name="Typology" dataDxfId="127"/>
+    <tableColumn id="2" xr3:uid="{4552E384-A064-4D7E-B638-6DC25252B385}" name="Floorspace m2" dataDxfId="126"/>
+    <tableColumn id="3" xr3:uid="{E22864B2-160F-4F3D-9491-0A60A9310C41}" name="Persons Per Dwelling - Private" dataDxfId="125"/>
+    <tableColumn id="4" xr3:uid="{0377E05F-6D73-4E82-AD3D-2AA209958578}" name="Persons Per Dwelling - Social/affordable" dataDxfId="124"/>
+    <tableColumn id="5" xr3:uid="{3D93BA7B-360E-4A20-BB94-AFEC8DAB2F05}" name="Council Tax per unit" dataDxfId="123"/>
+    <tableColumn id="6" xr3:uid="{E1042461-7B4B-4E4A-96C1-EA75409C533A}" name="Rent per social/MMR unit" dataDxfId="122"/>
+    <tableColumn id="7" xr3:uid="{56B6CFB9-570D-4CC0-9162-B0D0FCE94F69}" name="Private disposable income" dataDxfId="121"/>
+    <tableColumn id="8" xr3:uid="{CA5B102B-23EE-4F5D-853D-87DFD7D74ACA}" name="Social/affordable disposable income" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}" name="pop_employ" displayName="pop_employ" ref="A1:D6" totalsRowShown="0" headerRowDxfId="129" headerRowBorderDxfId="128" tableBorderDxfId="127" totalsRowBorderDxfId="126">
-  <autoFilter ref="A1:D6" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{947CE13C-D8BA-437F-95E3-C118D991F51E}" name="Parameter" dataDxfId="125"/>
-    <tableColumn id="2" xr3:uid="{07D50781-49CC-4BF6-8A8F-30D3D0C13A42}" name="Private" dataDxfId="124"/>
-    <tableColumn id="3" xr3:uid="{9642AD60-1B5A-4683-8E0B-12D1FE0BEBCA}" name="Social/affordable" dataDxfId="123"/>
-    <tableColumn id="4" xr3:uid="{D8D5E346-3E52-4B56-B72E-C2C8E3B487BA}" name="Units" dataDxfId="122"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}" name="pop_employ" displayName="pop_employ" ref="A1:E6" totalsRowShown="0" headerRowDxfId="119" headerRowBorderDxfId="118" tableBorderDxfId="117" totalsRowBorderDxfId="116">
+  <autoFilter ref="A1:E6" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{947CE13C-D8BA-437F-95E3-C118D991F51E}" name="Parameter" dataDxfId="115"/>
+    <tableColumn id="2" xr3:uid="{07D50781-49CC-4BF6-8A8F-30D3D0C13A42}" name="Private" dataDxfId="114"/>
+    <tableColumn id="3" xr3:uid="{9642AD60-1B5A-4683-8E0B-12D1FE0BEBCA}" name="Social/affordable" dataDxfId="113"/>
+    <tableColumn id="5" xr3:uid="{E72D4F67-11C4-42E3-B5A3-627689ABEEC2}" name="Older person" dataDxfId="112"/>
+    <tableColumn id="4" xr3:uid="{D8D5E346-3E52-4B56-B72E-C2C8E3B487BA}" name="Units" dataDxfId="111"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}" name="transport_modal" displayName="transport_modal" ref="A1:H9" totalsRowShown="0" headerRowDxfId="121" dataDxfId="119" headerRowBorderDxfId="120" tableBorderDxfId="118" totalsRowBorderDxfId="117">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}" name="transport_modal" displayName="transport_modal" ref="A1:H9" totalsRowShown="0" headerRowDxfId="110" dataDxfId="108" headerRowBorderDxfId="109" tableBorderDxfId="107" totalsRowBorderDxfId="106">
   <autoFilter ref="A1:H9" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{51D80002-D764-4804-8EC7-BF057B59E144}" name="Mode" dataDxfId="116"/>
-    <tableColumn id="2" xr3:uid="{632F4F89-D565-43F4-8508-41B297AC72E4}" name="Baseline share" dataDxfId="115"/>
-    <tableColumn id="3" xr3:uid="{F88145F9-8928-434C-8CDB-20D90AA0024C}" name="TCL Good" dataDxfId="114"/>
-    <tableColumn id="4" xr3:uid="{B0EC6125-F09D-4332-8FAF-A316F08C437C}" name="TCL Average" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{5AF3B7FB-6119-4BB3-BE48-1C87DAEBA045}" name="TCL Limited" dataDxfId="112"/>
-    <tableColumn id="6" xr3:uid="{28476781-DBA7-44F7-8DFF-F6C7E20BF879}" name="Baseline km" dataDxfId="111"/>
-    <tableColumn id="7" xr3:uid="{15EB3372-9D4F-46B3-A45C-B008382479FA}" name="Emission factor kgCO2e/pkm" dataDxfId="110"/>
-    <tableColumn id="8" xr3:uid="{7C2A1136-FFE8-4A44-AC30-D20CEB0F77DF}" name="Speed km/h" dataDxfId="109"/>
+    <tableColumn id="1" xr3:uid="{51D80002-D764-4804-8EC7-BF057B59E144}" name="Mode" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{632F4F89-D565-43F4-8508-41B297AC72E4}" name="Baseline share" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{F88145F9-8928-434C-8CDB-20D90AA0024C}" name="TCL Good" dataDxfId="103"/>
+    <tableColumn id="4" xr3:uid="{B0EC6125-F09D-4332-8FAF-A316F08C437C}" name="TCL Average" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{5AF3B7FB-6119-4BB3-BE48-1C87DAEBA045}" name="TCL Limited" dataDxfId="101"/>
+    <tableColumn id="6" xr3:uid="{28476781-DBA7-44F7-8DFF-F6C7E20BF879}" name="Baseline km" dataDxfId="100"/>
+    <tableColumn id="7" xr3:uid="{15EB3372-9D4F-46B3-A45C-B008382479FA}" name="Emission factor kgCO2e/pkm" dataDxfId="99"/>
+    <tableColumn id="8" xr3:uid="{7C2A1136-FFE8-4A44-AC30-D20CEB0F77DF}" name="Speed km/h" dataDxfId="98"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}" name="carbon" displayName="carbon" ref="A1:F4" totalsRowShown="0" headerRowDxfId="108" dataDxfId="106" headerRowBorderDxfId="107" tableBorderDxfId="105" totalsRowBorderDxfId="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}" name="carbon" displayName="carbon" ref="A1:F4" totalsRowShown="0" headerRowDxfId="97" dataDxfId="95" headerRowBorderDxfId="96" tableBorderDxfId="94" totalsRowBorderDxfId="93">
   <autoFilter ref="A1:F4" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{80B2580A-D788-4184-8B9B-91481871C1B1}" name="Development type" dataDxfId="103"/>
-    <tableColumn id="2" xr3:uid="{E2B4663C-5E14-40B1-B0E0-9F536D5994B1}" name="Low upfront" dataDxfId="102"/>
-    <tableColumn id="3" xr3:uid="{4F8B9403-C34D-4A52-AFD9-86BB230C316D}" name="Medium upfront" dataDxfId="101"/>
-    <tableColumn id="4" xr3:uid="{148042E5-61B0-4045-9632-78DA909DE42D}" name="High upfront" dataDxfId="100"/>
-    <tableColumn id="5" xr3:uid="{8A4AFD31-51B7-45FE-8D58-B6C8F3E1E731}" name="Baseline comparator" dataDxfId="99"/>
-    <tableColumn id="6" xr3:uid="{C11B7004-AD50-4B91-A6AC-2CD2E104AC48}" name="End of life factor" dataDxfId="98"/>
+    <tableColumn id="1" xr3:uid="{80B2580A-D788-4184-8B9B-91481871C1B1}" name="Development type" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{E2B4663C-5E14-40B1-B0E0-9F536D5994B1}" name="Low upfront" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{4F8B9403-C34D-4A52-AFD9-86BB230C316D}" name="Medium upfront" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{148042E5-61B0-4045-9632-78DA909DE42D}" name="High upfront" dataDxfId="89"/>
+    <tableColumn id="5" xr3:uid="{8A4AFD31-51B7-45FE-8D58-B6C8F3E1E731}" name="Baseline comparator" dataDxfId="88"/>
+    <tableColumn id="6" xr3:uid="{C11B7004-AD50-4B91-A6AC-2CD2E104AC48}" name="End of life factor" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}" name="environ_wellbeingTable6" displayName="environ_wellbeingTable6" ref="A1:E5" totalsRowShown="0" headerRowDxfId="97" headerRowBorderDxfId="96" tableBorderDxfId="95" totalsRowBorderDxfId="94">
-  <autoFilter ref="A1:E5" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}" name="environ_wellbeingTable6" displayName="environ_wellbeingTable6" ref="A1:E6" totalsRowShown="0" headerRowDxfId="86" headerRowBorderDxfId="85" tableBorderDxfId="84" totalsRowBorderDxfId="83">
+  <autoFilter ref="A1:E6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{04476D43-8F73-422A-9656-FA2B9CD22585}" name="Parameter" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{76480CDF-9E60-4089-A0A3-B5493DDC105F}" name="Lower scale impact" dataDxfId="92"/>
+    <tableColumn id="1" xr3:uid="{04476D43-8F73-422A-9656-FA2B9CD22585}" name="Parameter" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{76480CDF-9E60-4089-A0A3-B5493DDC105F}" name="Lower scale impact" dataDxfId="81"/>
     <tableColumn id="3" xr3:uid="{AB078BD6-DFAE-44D5-A871-78C491E01176}" name="Central impact"/>
     <tableColumn id="4" xr3:uid="{75FA526C-FBEE-4599-B606-702D6554E485}" name="Higher scale impact"/>
-    <tableColumn id="5" xr3:uid="{0BDF18F5-C495-4B11-AD1B-3043B7B15F46}" name="Units" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{0BDF18F5-C495-4B11-AD1B-3043B7B15F46}" name="Units" dataDxfId="80"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}" name="active_travel" displayName="active_travel" ref="A1:G4" totalsRowShown="0" headerRowDxfId="90" dataDxfId="88" headerRowBorderDxfId="89" tableBorderDxfId="87" totalsRowBorderDxfId="86">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}" name="active_travel" displayName="active_travel" ref="A1:G4" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76" totalsRowBorderDxfId="75">
   <autoFilter ref="A1:G4" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AD78C056-5CC9-4CD9-B25A-9E1FDA7619ED}" name="Accessibility" dataDxfId="85"/>
-    <tableColumn id="2" xr3:uid="{DDB6924C-0BED-4161-92F2-8EF3A236C4E5}" name="Walking uplift" dataDxfId="84"/>
-    <tableColumn id="3" xr3:uid="{9C68EE70-0111-4A45-8C9E-3C0000BE8EB3}" name="Cycling uplift" dataDxfId="83"/>
-    <tableColumn id="4" xr3:uid="{727BFA19-FC13-457E-A671-2032BFC507A9}" name="Minutes uplift" dataDxfId="82"/>
-    <tableColumn id="5" xr3:uid="{4EF746B4-929E-4ADE-9844-064C65AA8AF6}" name="Baseline meeting 150 mins (high deprivation)" dataDxfId="81"/>
-    <tableColumn id="6" xr3:uid="{A508C7D2-8286-46AA-AE93-0CFD202BABC6}" name="Baseline meeting 150 mins (average deprivation)" dataDxfId="80"/>
-    <tableColumn id="7" xr3:uid="{DA5F9070-A695-4818-AAC9-61F124AC7F92}" name="Baseline meeting 150 mins (low deprivation)" dataDxfId="79"/>
+    <tableColumn id="1" xr3:uid="{AD78C056-5CC9-4CD9-B25A-9E1FDA7619ED}" name="Accessibility" dataDxfId="74"/>
+    <tableColumn id="2" xr3:uid="{DDB6924C-0BED-4161-92F2-8EF3A236C4E5}" name="Walking uplift" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{9C68EE70-0111-4A45-8C9E-3C0000BE8EB3}" name="Cycling uplift" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{727BFA19-FC13-457E-A671-2032BFC507A9}" name="Minutes uplift" dataDxfId="71"/>
+    <tableColumn id="5" xr3:uid="{4EF746B4-929E-4ADE-9844-064C65AA8AF6}" name="Baseline meeting 150 mins (high deprivation)" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{A508C7D2-8286-46AA-AE93-0CFD202BABC6}" name="Baseline meeting 150 mins (average deprivation)" dataDxfId="69"/>
+    <tableColumn id="7" xr3:uid="{DA5F9070-A695-4818-AAC9-61F124AC7F92}" name="Baseline meeting 150 mins (low deprivation)" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}" name="crime" displayName="crime" ref="A1:D5" totalsRowShown="0" headerRowDxfId="78" headerRowBorderDxfId="77" tableBorderDxfId="76" totalsRowBorderDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}" name="crime" displayName="crime" ref="A1:D5" totalsRowShown="0" headerRowDxfId="67" headerRowBorderDxfId="66" tableBorderDxfId="65" totalsRowBorderDxfId="64">
   <autoFilter ref="A1:D5" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{907E3F67-1965-41D5-8DDD-707389C0597D}" name="Category" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{02A1EC8D-CE03-4112-AF55-3E5058D292AE}" name="Rate per 1,000" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{C292AD1E-37A6-4421-A549-FB7A56194F0B}" name="Cost per incident" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{7F206B66-30F3-4010-AC15-A9AFDE66E061}" name="Reduction rate" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{907E3F67-1965-41D5-8DDD-707389C0597D}" name="Category" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{02A1EC8D-CE03-4112-AF55-3E5058D292AE}" name="Rate per 1,000" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{C292AD1E-37A6-4421-A549-FB7A56194F0B}" name="Cost per incident" dataDxfId="61"/>
+    <tableColumn id="4" xr3:uid="{7F206B66-30F3-4010-AC15-A9AFDE66E061}" name="Reduction rate" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}" name="economic_coeff" displayName="economic_coeff" ref="A1:C8" totalsRowShown="0" headerRowDxfId="70" headerRowBorderDxfId="69" tableBorderDxfId="68" totalsRowBorderDxfId="67">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}" name="economic_coeff" displayName="economic_coeff" ref="A1:C8" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57" totalsRowBorderDxfId="56">
   <autoFilter ref="A1:C8" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B3E4FC91-3B70-4B5F-BE4B-3D95311501D9}" name="Parameter" dataDxfId="66"/>
-    <tableColumn id="2" xr3:uid="{8E11059B-045B-4658-BEA4-ACFA568B296F}" name="Value" dataDxfId="65"/>
-    <tableColumn id="3" xr3:uid="{97CBA549-19DB-408B-AA6F-BDFA09076EB0}" name="Units" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{B3E4FC91-3B70-4B5F-BE4B-3D95311501D9}" name="Parameter" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{8E11059B-045B-4658-BEA4-ACFA568B296F}" name="Value" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{97CBA549-19DB-408B-AA6F-BDFA09076EB0}" name="Units" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6038,7 +6106,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>122</v>
       </c>
@@ -6046,7 +6114,7 @@
         <v>123</v>
       </c>
       <c r="C2" s="4">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="D2" s="4">
         <v>0.15</v>
@@ -6058,7 +6126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>122</v>
       </c>
@@ -6066,7 +6134,7 @@
         <v>124</v>
       </c>
       <c r="C3" s="4">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="D3" s="4">
         <v>7.4999999999999997E-2</v>
@@ -6078,7 +6146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>122</v>
       </c>
@@ -6098,7 +6166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>126</v>
       </c>
@@ -6106,10 +6174,10 @@
         <v>123</v>
       </c>
       <c r="C5" s="4">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D5" s="4">
-        <v>0.55000000000000004</v>
+        <v>0.35</v>
       </c>
       <c r="E5" s="4">
         <v>0</v>
@@ -6118,7 +6186,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>126</v>
       </c>
@@ -6126,10 +6194,10 @@
         <v>124</v>
       </c>
       <c r="C6" s="4">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="D6" s="4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="E6" s="4">
         <v>0</v>
@@ -6138,7 +6206,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>126</v>
       </c>
@@ -6158,7 +6226,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>127</v>
       </c>
@@ -6166,10 +6234,10 @@
         <v>123</v>
       </c>
       <c r="C8" s="4">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D8" s="4">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="E8" s="4">
         <v>0.6</v>
@@ -6178,7 +6246,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>127</v>
       </c>
@@ -6186,10 +6254,10 @@
         <v>124</v>
       </c>
       <c r="C9" s="4">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="D9" s="4">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E9" s="4">
         <v>0.4</v>
@@ -6198,7 +6266,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>127</v>
       </c>
@@ -6238,7 +6306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>128</v>
       </c>
@@ -6459,7 +6527,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD964448-B0BD-44C9-9E47-73F1B6F59CE2}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.5546875" customWidth="1"/>
@@ -6561,17 +6629,31 @@
         <v>152</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="B8" s="66">
+        <v>250</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>190</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="40" t="s">
         <v>153</v>
       </c>
-      <c r="B8" s="53">
+      <c r="B9" s="53">
         <v>1.208</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C9" s="42" t="s">
         <v>99</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D9" s="43" t="s">
         <v>152</v>
       </c>
     </row>
@@ -7049,15 +7131,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31A8A6C9-C19C-4552-9F1A-64DF3651C468}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
     <col min="2" max="2" width="15.6640625" customWidth="1"/>
-    <col min="3" max="3" width="25.109375" customWidth="1"/>
+    <col min="3" max="4" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -7068,10 +7150,13 @@
         <v>35</v>
       </c>
       <c r="D1" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="E1" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -7081,11 +7166,14 @@
       <c r="C2" s="4">
         <v>0.2</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="21">
+        <v>0.1</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>37</v>
       </c>
@@ -7095,11 +7183,14 @@
       <c r="C3" s="4">
         <v>0.6</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="21">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>38</v>
       </c>
@@ -7109,11 +7200,14 @@
       <c r="C4" s="4">
         <v>0.2</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="21">
+        <v>0.7</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>39</v>
       </c>
@@ -7123,11 +7217,14 @@
       <c r="C5" s="4">
         <v>0.5</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>40</v>
       </c>
@@ -7137,7 +7234,10 @@
       <c r="C6" s="18">
         <v>0.5</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="22">
+        <v>0.5</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>14</v>
       </c>
     </row>
@@ -7508,7 +7608,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5577B706-CCCE-4547-9663-A50B7359574D}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.21875" customWidth="1"/>
@@ -7552,18 +7652,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B3" s="23">
-        <v>8.3333000000000001E-3</v>
+        <v>188</v>
+      </c>
+      <c r="B3" s="65">
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="C3" s="23">
-        <v>1.666666E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="D3" s="23">
-        <v>3.3E-3</v>
+        <v>6.6E-3</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>70</v>
@@ -7571,27 +7671,44 @@
     </row>
     <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="23">
+        <v>8.3333000000000001E-3</v>
+      </c>
+      <c r="C4" s="23">
+        <v>1.666666E-3</v>
+      </c>
+      <c r="D4" s="23">
+        <v>3.3E-3</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B5" s="23">
         <v>0.05</v>
       </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="6" t="s">
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="6" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+    <row r="6" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B6" s="25">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="13" t="s">
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="13" t="s">
         <v>73</v>
       </c>
     </row>

--- a/data/assumptions.xlsx
+++ b/data/assumptions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ekosltd-my.sharepoint.com/personal/alessia_biris_ekos_co_uk/Documents/TCL/code_dashboard/v2/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{FA218BAD-3EBA-47B7-9DEF-468792D266E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FA303A8-BBEE-4BD1-8454-7FFFA21B5672}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{FA218BAD-3EBA-47B7-9DEF-468792D266E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BEDB1A4-74A1-481E-B850-1F6C3745C7BE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="9" activeTab="13" xr2:uid="{5C67809F-44A3-4AFA-BBD2-6581972C325D}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="17" xr2:uid="{5C67809F-44A3-4AFA-BBD2-6581972C325D}"/>
   </bookViews>
   <sheets>
     <sheet name="general_parameters" sheetId="1" r:id="rId1"/>
@@ -1622,20 +1622,13 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="thin">
+        <top style="medium">
           <color indexed="64"/>
         </top>
         <bottom style="medium">
@@ -1729,6 +1722,42 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="170" formatCode="0.0%"/>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1782,13 +1811,20 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <left style="medium">
           <color indexed="64"/>
         </left>
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="medium">
+        <top style="thin">
           <color indexed="64"/>
         </top>
         <bottom style="medium">
@@ -1844,12 +1880,19 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="169" formatCode="0.0\x"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1877,12 +1920,19 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1912,13 +1962,19 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="170" formatCode="0.0%"/>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1948,12 +2004,89 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
         <color theme="1"/>
         <name val="Avenir Next LT Pro"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1993,6 +2126,31 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF666666"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF2F2F2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
@@ -2001,22 +2159,28 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFDCE6F1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4845,19 +5009,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="169" formatCode="0.0\x"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4885,19 +5042,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -4927,131 +5077,12 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="166" formatCode="0.0%;[Red]\(0.0%\);\-"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
         <color theme="1"/>
         <name val="Avenir Next LT Pro"/>
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -5091,31 +5122,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF666666"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
@@ -5124,28 +5130,22 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFDCE6F1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -5170,86 +5170,82 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}" name="general_parameters" displayName="general_parameters" ref="A1:D8" totalsRowShown="0" headerRowDxfId="139" headerRowBorderDxfId="138" tableBorderDxfId="137" totalsRowBorderDxfId="136">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}" name="general_parameters" displayName="general_parameters" ref="A1:D8" totalsRowShown="0" headerRowDxfId="143" headerRowBorderDxfId="142" tableBorderDxfId="141" totalsRowBorderDxfId="140">
   <autoFilter ref="A1:D8" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BF4A73EA-A313-4283-BE5C-5B9F6C2039F3}" name="Parameter" dataDxfId="135"/>
+    <tableColumn id="1" xr3:uid="{BF4A73EA-A313-4283-BE5C-5B9F6C2039F3}" name="Parameter" dataDxfId="139"/>
     <tableColumn id="2" xr3:uid="{2168A1D6-1F00-420A-AE49-628879EF67CF}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{EE2AD78A-DCFF-47D8-A4FD-47301D7A564F}" name="Units" dataDxfId="134"/>
-    <tableColumn id="4" xr3:uid="{F7910500-F089-4E59-9AC8-5734EF06B071}" name="Source / note" dataDxfId="133"/>
+    <tableColumn id="3" xr3:uid="{EE2AD78A-DCFF-47D8-A4FD-47301D7A564F}" name="Units" dataDxfId="138"/>
+    <tableColumn id="4" xr3:uid="{F7910500-F089-4E59-9AC8-5734EF06B071}" name="Source / note" dataDxfId="137"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}" name="household_spend" displayName="household_spend" ref="A1:E11" totalsRowShown="0" headerRowDxfId="52" dataDxfId="50" headerRowBorderDxfId="51" tableBorderDxfId="49" totalsRowBorderDxfId="48">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}" name="household_spend" displayName="household_spend" ref="A1:E11" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53" totalsRowBorderDxfId="52">
   <autoFilter ref="A1:E11" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9A4690EE-FA56-405E-A30D-875570657134}" name="Typology / tenure" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{E91F277E-06CE-4EDB-8543-29E44E82DEA7}" name="Upper" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{1EAAF470-471D-4B0C-A575-DFBD58AEA1B8}" name="Central" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{57C7CBC2-465E-4D9C-862C-8B255FF6A5B2}" name="Lower" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{2AC2BF98-5348-4DE0-93F2-91C9D65F223E}" name="Units" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{9A4690EE-FA56-405E-A30D-875570657134}" name="Typology / tenure" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{E91F277E-06CE-4EDB-8543-29E44E82DEA7}" name="Upper" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{1EAAF470-471D-4B0C-A575-DFBD58AEA1B8}" name="Central" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{57C7CBC2-465E-4D9C-862C-8B255FF6A5B2}" name="Lower" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{2AC2BF98-5348-4DE0-93F2-91C9D65F223E}" name="Units" dataDxfId="47"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}" name="additionality_mappings" displayName="additionality_mappings" ref="A1:F16" totalsRowShown="0" headerRowDxfId="150" dataDxfId="148" headerRowBorderDxfId="149" tableBorderDxfId="147" totalsRowBorderDxfId="146">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}" name="additionality_mappings" displayName="additionality_mappings" ref="A1:F16" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
   <autoFilter ref="A1:F16" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E3A723FA-457B-4EFE-9E92-EB013E337B59}" name="Group" dataDxfId="145"/>
-    <tableColumn id="2" xr3:uid="{02D51F27-6686-45C8-B830-EE4683B203DE}" name="Scenario" dataDxfId="144"/>
-    <tableColumn id="3" xr3:uid="{141761B2-F5F5-4B9A-8B3E-DC8AC7A74CBC}" name="Deadweight" dataDxfId="143"/>
-    <tableColumn id="4" xr3:uid="{73079F49-39D1-41A2-AF81-9562C0ADE495}" name="Displacement" dataDxfId="142"/>
-    <tableColumn id="5" xr3:uid="{BF1D37EB-AE48-4C08-9998-896BCDE53C45}" name="Leakage" dataDxfId="141"/>
-    <tableColumn id="6" xr3:uid="{343EC36C-1426-4634-AD97-7726BDCCA977}" name="Multiplier" dataDxfId="140"/>
+    <tableColumn id="1" xr3:uid="{E3A723FA-457B-4EFE-9E92-EB013E337B59}" name="Group" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{02D51F27-6686-45C8-B830-EE4683B203DE}" name="Scenario" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{141761B2-F5F5-4B9A-8B3E-DC8AC7A74CBC}" name="Deadweight" dataDxfId="39"/>
+    <tableColumn id="4" xr3:uid="{73079F49-39D1-41A2-AF81-9562C0ADE495}" name="Displacement" dataDxfId="38"/>
+    <tableColumn id="5" xr3:uid="{BF1D37EB-AE48-4C08-9998-896BCDE53C45}" name="Leakage" dataDxfId="37"/>
+    <tableColumn id="6" xr3:uid="{343EC36C-1426-4634-AD97-7726BDCCA977}" name="Multiplier" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{B1ED9103-DDDE-47B1-8810-5356D0BC801A}" name="discounting" displayName="discounting" ref="A1:D3" totalsRowShown="0" headerRowDxfId="42" headerRowBorderDxfId="41" tableBorderDxfId="40" totalsRowBorderDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{B1ED9103-DDDE-47B1-8810-5356D0BC801A}" name="discounting" displayName="discounting" ref="A1:D3" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
   <autoFilter ref="A1:D3" xr:uid="{B1ED9103-DDDE-47B1-8810-5356D0BC801A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C9D1B6E6-554B-4728-999B-F79940D1548F}" name="Parameter" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{9CC8EED5-22B9-4B6C-ABA0-C94CA361A8EB}" name="Value" dataDxfId="37"/>
-    <tableColumn id="3" xr3:uid="{DF9EDA1C-294C-452B-BFF2-26FBD630BCD3}" name="Unit" dataDxfId="36"/>
-    <tableColumn id="4" xr3:uid="{D5D8E8F0-51CC-4FDB-ABC4-1CE5C67CF3DC}" name="Source" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{C9D1B6E6-554B-4728-999B-F79940D1548F}" name="Parameter" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{9CC8EED5-22B9-4B6C-ABA0-C94CA361A8EB}" name="Value" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{DF9EDA1C-294C-452B-BFF2-26FBD630BCD3}" name="Unit" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{D5D8E8F0-51CC-4FDB-ABC4-1CE5C67CF3DC}" name="Source" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{6423D1D0-30EB-48F7-8293-4EDC0FFE06C1}" name="discounting_by_impact" displayName="discounting_by_impact" ref="A1:D4" totalsRowShown="0" headerRowDxfId="34" headerRowBorderDxfId="33" tableBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{6423D1D0-30EB-48F7-8293-4EDC0FFE06C1}" name="discounting_by_impact" displayName="discounting_by_impact" ref="A1:D4" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="26" tableBorderDxfId="25">
   <autoFilter ref="A1:D4" xr:uid="{6423D1D0-30EB-48F7-8293-4EDC0FFE06C1}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BAA839D6-42E3-4FD9-8386-2108D73EF939}" name="Impact" dataDxfId="31"/>
+    <tableColumn id="1" xr3:uid="{BAA839D6-42E3-4FD9-8386-2108D73EF939}" name="Impact" dataDxfId="24"/>
     <tableColumn id="2" xr3:uid="{34EDF934-C8FE-4FFD-9217-6E193C221B78}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{6516570E-DCB9-4F5C-8D62-991AA6C746A7}" name="Unit" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{B4F1FF20-BFB8-46B8-A719-D89B829DB05B}" name="Notes" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{6516570E-DCB9-4F5C-8D62-991AA6C746A7}" name="Unit" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{B4F1FF20-BFB8-46B8-A719-D89B829DB05B}" name="Notes" dataDxfId="22"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}" name="land_infra_mult" displayName="land_infra_mult" ref="A1:D9" totalsRowShown="0" headerRowDxfId="28" headerRowBorderDxfId="27" tableBorderDxfId="26" totalsRowBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}" name="land_infra_mult" displayName="land_infra_mult" ref="A1:D9" totalsRowShown="0" headerRowDxfId="150" headerRowBorderDxfId="149" tableBorderDxfId="148" totalsRowBorderDxfId="147">
   <autoFilter ref="A1:D9" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7FD0A6E6-1B0A-4FC7-81EC-4DD560B478DC}" name="Parameter" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{7FD0A6E6-1B0A-4FC7-81EC-4DD560B478DC}" name="Parameter" dataDxfId="146"/>
     <tableColumn id="2" xr3:uid="{A7B1CC4E-78DF-4D14-A750-3E88F52FAF2A}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{2E3AE3B4-C3F9-4F53-873A-03E831ED79B8}" name="Unit" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{4BF2B9CD-2B84-4D85-BBB6-91888AED0426}" name="Notes" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{2E3AE3B4-C3F9-4F53-873A-03E831ED79B8}" name="Unit" dataDxfId="145"/>
+    <tableColumn id="4" xr3:uid="{4BF2B9CD-2B84-4D85-BBB6-91888AED0426}" name="Notes" dataDxfId="144"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5304,118 +5300,118 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}" name="dwellingbytypology" displayName="dwellingbytypology" ref="A1:H6" totalsRowShown="0" headerRowDxfId="132" dataDxfId="130" headerRowBorderDxfId="131" tableBorderDxfId="129" totalsRowBorderDxfId="128">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}" name="dwellingbytypology" displayName="dwellingbytypology" ref="A1:H6" totalsRowShown="0" headerRowDxfId="136" dataDxfId="134" headerRowBorderDxfId="135" tableBorderDxfId="133" totalsRowBorderDxfId="132">
   <autoFilter ref="A1:H6" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AF5B1002-ACF0-443F-BA91-D855456C8E2D}" name="Typology" dataDxfId="127"/>
-    <tableColumn id="2" xr3:uid="{4552E384-A064-4D7E-B638-6DC25252B385}" name="Floorspace m2" dataDxfId="126"/>
-    <tableColumn id="3" xr3:uid="{E22864B2-160F-4F3D-9491-0A60A9310C41}" name="Persons Per Dwelling - Private" dataDxfId="125"/>
-    <tableColumn id="4" xr3:uid="{0377E05F-6D73-4E82-AD3D-2AA209958578}" name="Persons Per Dwelling - Social/affordable" dataDxfId="124"/>
-    <tableColumn id="5" xr3:uid="{3D93BA7B-360E-4A20-BB94-AFEC8DAB2F05}" name="Council Tax per unit" dataDxfId="123"/>
-    <tableColumn id="6" xr3:uid="{E1042461-7B4B-4E4A-96C1-EA75409C533A}" name="Rent per social/MMR unit" dataDxfId="122"/>
-    <tableColumn id="7" xr3:uid="{56B6CFB9-570D-4CC0-9162-B0D0FCE94F69}" name="Private disposable income" dataDxfId="121"/>
-    <tableColumn id="8" xr3:uid="{CA5B102B-23EE-4F5D-853D-87DFD7D74ACA}" name="Social/affordable disposable income" dataDxfId="120"/>
+    <tableColumn id="1" xr3:uid="{AF5B1002-ACF0-443F-BA91-D855456C8E2D}" name="Typology" dataDxfId="131"/>
+    <tableColumn id="2" xr3:uid="{4552E384-A064-4D7E-B638-6DC25252B385}" name="Floorspace m2" dataDxfId="130"/>
+    <tableColumn id="3" xr3:uid="{E22864B2-160F-4F3D-9491-0A60A9310C41}" name="Persons Per Dwelling - Private" dataDxfId="129"/>
+    <tableColumn id="4" xr3:uid="{0377E05F-6D73-4E82-AD3D-2AA209958578}" name="Persons Per Dwelling - Social/affordable" dataDxfId="128"/>
+    <tableColumn id="5" xr3:uid="{3D93BA7B-360E-4A20-BB94-AFEC8DAB2F05}" name="Council Tax per unit" dataDxfId="127"/>
+    <tableColumn id="6" xr3:uid="{E1042461-7B4B-4E4A-96C1-EA75409C533A}" name="Rent per social/MMR unit" dataDxfId="126"/>
+    <tableColumn id="7" xr3:uid="{56B6CFB9-570D-4CC0-9162-B0D0FCE94F69}" name="Private disposable income" dataDxfId="125"/>
+    <tableColumn id="8" xr3:uid="{CA5B102B-23EE-4F5D-853D-87DFD7D74ACA}" name="Social/affordable disposable income" dataDxfId="124"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}" name="pop_employ" displayName="pop_employ" ref="A1:E6" totalsRowShown="0" headerRowDxfId="119" headerRowBorderDxfId="118" tableBorderDxfId="117" totalsRowBorderDxfId="116">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}" name="pop_employ" displayName="pop_employ" ref="A1:E6" totalsRowShown="0" headerRowDxfId="123" headerRowBorderDxfId="122" tableBorderDxfId="121" totalsRowBorderDxfId="120">
   <autoFilter ref="A1:E6" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{947CE13C-D8BA-437F-95E3-C118D991F51E}" name="Parameter" dataDxfId="115"/>
-    <tableColumn id="2" xr3:uid="{07D50781-49CC-4BF6-8A8F-30D3D0C13A42}" name="Private" dataDxfId="114"/>
-    <tableColumn id="3" xr3:uid="{9642AD60-1B5A-4683-8E0B-12D1FE0BEBCA}" name="Social/affordable" dataDxfId="113"/>
-    <tableColumn id="5" xr3:uid="{E72D4F67-11C4-42E3-B5A3-627689ABEEC2}" name="Older person" dataDxfId="112"/>
-    <tableColumn id="4" xr3:uid="{D8D5E346-3E52-4B56-B72E-C2C8E3B487BA}" name="Units" dataDxfId="111"/>
+    <tableColumn id="1" xr3:uid="{947CE13C-D8BA-437F-95E3-C118D991F51E}" name="Parameter" dataDxfId="119"/>
+    <tableColumn id="2" xr3:uid="{07D50781-49CC-4BF6-8A8F-30D3D0C13A42}" name="Private" dataDxfId="118"/>
+    <tableColumn id="3" xr3:uid="{9642AD60-1B5A-4683-8E0B-12D1FE0BEBCA}" name="Social/affordable" dataDxfId="117"/>
+    <tableColumn id="5" xr3:uid="{E72D4F67-11C4-42E3-B5A3-627689ABEEC2}" name="Older person" dataDxfId="116"/>
+    <tableColumn id="4" xr3:uid="{D8D5E346-3E52-4B56-B72E-C2C8E3B487BA}" name="Units" dataDxfId="115"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}" name="transport_modal" displayName="transport_modal" ref="A1:H9" totalsRowShown="0" headerRowDxfId="110" dataDxfId="108" headerRowBorderDxfId="109" tableBorderDxfId="107" totalsRowBorderDxfId="106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}" name="transport_modal" displayName="transport_modal" ref="A1:H9" totalsRowShown="0" headerRowDxfId="114" dataDxfId="112" headerRowBorderDxfId="113" tableBorderDxfId="111" totalsRowBorderDxfId="110">
   <autoFilter ref="A1:H9" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{51D80002-D764-4804-8EC7-BF057B59E144}" name="Mode" dataDxfId="105"/>
-    <tableColumn id="2" xr3:uid="{632F4F89-D565-43F4-8508-41B297AC72E4}" name="Baseline share" dataDxfId="104"/>
-    <tableColumn id="3" xr3:uid="{F88145F9-8928-434C-8CDB-20D90AA0024C}" name="TCL Good" dataDxfId="103"/>
-    <tableColumn id="4" xr3:uid="{B0EC6125-F09D-4332-8FAF-A316F08C437C}" name="TCL Average" dataDxfId="102"/>
-    <tableColumn id="5" xr3:uid="{5AF3B7FB-6119-4BB3-BE48-1C87DAEBA045}" name="TCL Limited" dataDxfId="101"/>
-    <tableColumn id="6" xr3:uid="{28476781-DBA7-44F7-8DFF-F6C7E20BF879}" name="Baseline km" dataDxfId="100"/>
-    <tableColumn id="7" xr3:uid="{15EB3372-9D4F-46B3-A45C-B008382479FA}" name="Emission factor kgCO2e/pkm" dataDxfId="99"/>
-    <tableColumn id="8" xr3:uid="{7C2A1136-FFE8-4A44-AC30-D20CEB0F77DF}" name="Speed km/h" dataDxfId="98"/>
+    <tableColumn id="1" xr3:uid="{51D80002-D764-4804-8EC7-BF057B59E144}" name="Mode" dataDxfId="109"/>
+    <tableColumn id="2" xr3:uid="{632F4F89-D565-43F4-8508-41B297AC72E4}" name="Baseline share" dataDxfId="108"/>
+    <tableColumn id="3" xr3:uid="{F88145F9-8928-434C-8CDB-20D90AA0024C}" name="TCL Good" dataDxfId="107"/>
+    <tableColumn id="4" xr3:uid="{B0EC6125-F09D-4332-8FAF-A316F08C437C}" name="TCL Average" dataDxfId="106"/>
+    <tableColumn id="5" xr3:uid="{5AF3B7FB-6119-4BB3-BE48-1C87DAEBA045}" name="TCL Limited" dataDxfId="105"/>
+    <tableColumn id="6" xr3:uid="{28476781-DBA7-44F7-8DFF-F6C7E20BF879}" name="Baseline km" dataDxfId="104"/>
+    <tableColumn id="7" xr3:uid="{15EB3372-9D4F-46B3-A45C-B008382479FA}" name="Emission factor kgCO2e/pkm" dataDxfId="103"/>
+    <tableColumn id="8" xr3:uid="{7C2A1136-FFE8-4A44-AC30-D20CEB0F77DF}" name="Speed km/h" dataDxfId="102"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}" name="carbon" displayName="carbon" ref="A1:F4" totalsRowShown="0" headerRowDxfId="97" dataDxfId="95" headerRowBorderDxfId="96" tableBorderDxfId="94" totalsRowBorderDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}" name="carbon" displayName="carbon" ref="A1:F4" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" totalsRowBorderDxfId="97">
   <autoFilter ref="A1:F4" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{80B2580A-D788-4184-8B9B-91481871C1B1}" name="Development type" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{E2B4663C-5E14-40B1-B0E0-9F536D5994B1}" name="Low upfront" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{4F8B9403-C34D-4A52-AFD9-86BB230C316D}" name="Medium upfront" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{148042E5-61B0-4045-9632-78DA909DE42D}" name="High upfront" dataDxfId="89"/>
-    <tableColumn id="5" xr3:uid="{8A4AFD31-51B7-45FE-8D58-B6C8F3E1E731}" name="Baseline comparator" dataDxfId="88"/>
-    <tableColumn id="6" xr3:uid="{C11B7004-AD50-4B91-A6AC-2CD2E104AC48}" name="End of life factor" dataDxfId="87"/>
+    <tableColumn id="1" xr3:uid="{80B2580A-D788-4184-8B9B-91481871C1B1}" name="Development type" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{E2B4663C-5E14-40B1-B0E0-9F536D5994B1}" name="Low upfront" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{4F8B9403-C34D-4A52-AFD9-86BB230C316D}" name="Medium upfront" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{148042E5-61B0-4045-9632-78DA909DE42D}" name="High upfront" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{8A4AFD31-51B7-45FE-8D58-B6C8F3E1E731}" name="Baseline comparator" dataDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{C11B7004-AD50-4B91-A6AC-2CD2E104AC48}" name="End of life factor" dataDxfId="91"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}" name="environ_wellbeingTable6" displayName="environ_wellbeingTable6" ref="A1:E6" totalsRowShown="0" headerRowDxfId="86" headerRowBorderDxfId="85" tableBorderDxfId="84" totalsRowBorderDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}" name="environ_wellbeingTable6" displayName="environ_wellbeingTable6" ref="A1:E6" totalsRowShown="0" headerRowDxfId="90" headerRowBorderDxfId="89" tableBorderDxfId="88" totalsRowBorderDxfId="87">
   <autoFilter ref="A1:E6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{04476D43-8F73-422A-9656-FA2B9CD22585}" name="Parameter" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{76480CDF-9E60-4089-A0A3-B5493DDC105F}" name="Lower scale impact" dataDxfId="81"/>
+    <tableColumn id="1" xr3:uid="{04476D43-8F73-422A-9656-FA2B9CD22585}" name="Parameter" dataDxfId="86"/>
+    <tableColumn id="2" xr3:uid="{76480CDF-9E60-4089-A0A3-B5493DDC105F}" name="Lower scale impact" dataDxfId="85"/>
     <tableColumn id="3" xr3:uid="{AB078BD6-DFAE-44D5-A871-78C491E01176}" name="Central impact"/>
     <tableColumn id="4" xr3:uid="{75FA526C-FBEE-4599-B606-702D6554E485}" name="Higher scale impact"/>
-    <tableColumn id="5" xr3:uid="{0BDF18F5-C495-4B11-AD1B-3043B7B15F46}" name="Units" dataDxfId="80"/>
+    <tableColumn id="5" xr3:uid="{0BDF18F5-C495-4B11-AD1B-3043B7B15F46}" name="Units" dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}" name="active_travel" displayName="active_travel" ref="A1:G4" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76" totalsRowBorderDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}" name="active_travel" displayName="active_travel" ref="A1:G4" totalsRowShown="0" headerRowDxfId="83" dataDxfId="81" headerRowBorderDxfId="82" tableBorderDxfId="80" totalsRowBorderDxfId="79">
   <autoFilter ref="A1:G4" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AD78C056-5CC9-4CD9-B25A-9E1FDA7619ED}" name="Accessibility" dataDxfId="74"/>
-    <tableColumn id="2" xr3:uid="{DDB6924C-0BED-4161-92F2-8EF3A236C4E5}" name="Walking uplift" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{9C68EE70-0111-4A45-8C9E-3C0000BE8EB3}" name="Cycling uplift" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{727BFA19-FC13-457E-A671-2032BFC507A9}" name="Minutes uplift" dataDxfId="71"/>
-    <tableColumn id="5" xr3:uid="{4EF746B4-929E-4ADE-9844-064C65AA8AF6}" name="Baseline meeting 150 mins (high deprivation)" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{A508C7D2-8286-46AA-AE93-0CFD202BABC6}" name="Baseline meeting 150 mins (average deprivation)" dataDxfId="69"/>
-    <tableColumn id="7" xr3:uid="{DA5F9070-A695-4818-AAC9-61F124AC7F92}" name="Baseline meeting 150 mins (low deprivation)" dataDxfId="68"/>
+    <tableColumn id="1" xr3:uid="{AD78C056-5CC9-4CD9-B25A-9E1FDA7619ED}" name="Accessibility" dataDxfId="78"/>
+    <tableColumn id="2" xr3:uid="{DDB6924C-0BED-4161-92F2-8EF3A236C4E5}" name="Walking uplift" dataDxfId="77"/>
+    <tableColumn id="3" xr3:uid="{9C68EE70-0111-4A45-8C9E-3C0000BE8EB3}" name="Cycling uplift" dataDxfId="76"/>
+    <tableColumn id="4" xr3:uid="{727BFA19-FC13-457E-A671-2032BFC507A9}" name="Minutes uplift" dataDxfId="75"/>
+    <tableColumn id="5" xr3:uid="{4EF746B4-929E-4ADE-9844-064C65AA8AF6}" name="Baseline meeting 150 mins (high deprivation)" dataDxfId="74"/>
+    <tableColumn id="6" xr3:uid="{A508C7D2-8286-46AA-AE93-0CFD202BABC6}" name="Baseline meeting 150 mins (average deprivation)" dataDxfId="73"/>
+    <tableColumn id="7" xr3:uid="{DA5F9070-A695-4818-AAC9-61F124AC7F92}" name="Baseline meeting 150 mins (low deprivation)" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}" name="crime" displayName="crime" ref="A1:D5" totalsRowShown="0" headerRowDxfId="67" headerRowBorderDxfId="66" tableBorderDxfId="65" totalsRowBorderDxfId="64">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}" name="crime" displayName="crime" ref="A1:D5" totalsRowShown="0" headerRowDxfId="71" headerRowBorderDxfId="70" tableBorderDxfId="69" totalsRowBorderDxfId="68">
   <autoFilter ref="A1:D5" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{907E3F67-1965-41D5-8DDD-707389C0597D}" name="Category" dataDxfId="63"/>
-    <tableColumn id="2" xr3:uid="{02A1EC8D-CE03-4112-AF55-3E5058D292AE}" name="Rate per 1,000" dataDxfId="62"/>
-    <tableColumn id="3" xr3:uid="{C292AD1E-37A6-4421-A549-FB7A56194F0B}" name="Cost per incident" dataDxfId="61"/>
-    <tableColumn id="4" xr3:uid="{7F206B66-30F3-4010-AC15-A9AFDE66E061}" name="Reduction rate" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{907E3F67-1965-41D5-8DDD-707389C0597D}" name="Category" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{02A1EC8D-CE03-4112-AF55-3E5058D292AE}" name="Rate per 1,000" dataDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{C292AD1E-37A6-4421-A549-FB7A56194F0B}" name="Cost per incident" dataDxfId="65"/>
+    <tableColumn id="4" xr3:uid="{7F206B66-30F3-4010-AC15-A9AFDE66E061}" name="Reduction rate" dataDxfId="64"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}" name="economic_coeff" displayName="economic_coeff" ref="A1:C8" totalsRowShown="0" headerRowDxfId="59" headerRowBorderDxfId="58" tableBorderDxfId="57" totalsRowBorderDxfId="56">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}" name="economic_coeff" displayName="economic_coeff" ref="A1:C8" totalsRowShown="0" headerRowDxfId="63" headerRowBorderDxfId="62" tableBorderDxfId="61" totalsRowBorderDxfId="60">
   <autoFilter ref="A1:C8" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B3E4FC91-3B70-4B5F-BE4B-3D95311501D9}" name="Parameter" dataDxfId="55"/>
-    <tableColumn id="2" xr3:uid="{8E11059B-045B-4658-BEA4-ACFA568B296F}" name="Value" dataDxfId="54"/>
-    <tableColumn id="3" xr3:uid="{97CBA549-19DB-408B-AA6F-BDFA09076EB0}" name="Units" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{B3E4FC91-3B70-4B5F-BE4B-3D95311501D9}" name="Parameter" dataDxfId="59"/>
+    <tableColumn id="2" xr3:uid="{8E11059B-045B-4658-BEA4-ACFA568B296F}" name="Value" dataDxfId="58"/>
+    <tableColumn id="3" xr3:uid="{97CBA549-19DB-408B-AA6F-BDFA09076EB0}" name="Units" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7669,18 +7665,18 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="23">
-        <v>8.3333000000000001E-3</v>
+      <c r="B4" s="65">
+        <v>1.6999999999999999E-3</v>
       </c>
       <c r="C4" s="23">
-        <v>1.666666E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="D4" s="23">
-        <v>3.3E-3</v>
+        <v>6.6E-3</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>70</v>

--- a/data/assumptions.xlsx
+++ b/data/assumptions.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ekosltd-my.sharepoint.com/personal/alessia_biris_ekos_co_uk/Documents/TCL/code_dashboard/v2/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Shared\onedrivefinal\2025\Live Jobs\SFT Town Centre Living\Logic model + impact framework\Final\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="8_{FA218BAD-3EBA-47B7-9DEF-468792D266E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BEDB1A4-74A1-481E-B850-1F6C3745C7BE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D446209-E906-4F6E-A845-5E0104DEF644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="12" activeTab="17" xr2:uid="{5C67809F-44A3-4AFA-BBD2-6581972C325D}"/>
+    <workbookView xWindow="-252" yWindow="696" windowWidth="13824" windowHeight="9864" firstSheet="4" activeTab="5" xr2:uid="{5C67809F-44A3-4AFA-BBD2-6581972C325D}"/>
   </bookViews>
   <sheets>
     <sheet name="general_parameters" sheetId="1" r:id="rId1"/>
@@ -1067,56 +1067,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
@@ -1249,6 +1199,166 @@
         <scheme val="none"/>
       </font>
       <numFmt numFmtId="172" formatCode="0.0"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Avenir Next LT Pro"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -5014,21 +5124,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
+      <numFmt numFmtId="164" formatCode="\£#,##0;[Red]&quot;(£&quot;#,##0\);\-"/>
     </dxf>
     <dxf>
       <font>
@@ -5047,63 +5143,6 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <border outline="0">
@@ -5113,48 +5152,9 @@
         <right style="medium">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="medium">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Avenir Next LT Pro"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -5171,117 +5171,117 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}" name="general_parameters" displayName="general_parameters" ref="A1:D8" totalsRowShown="0" headerRowDxfId="143" headerRowBorderDxfId="142" tableBorderDxfId="141" totalsRowBorderDxfId="140">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}" name="general_parameters" displayName="general_parameters" ref="A1:D8" totalsRowShown="0" headerRowDxfId="147" headerRowBorderDxfId="146" tableBorderDxfId="145" totalsRowBorderDxfId="144">
   <autoFilter ref="A1:D8" xr:uid="{5C45BCAE-2920-4A62-AF02-18762D92BA91}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BF4A73EA-A313-4283-BE5C-5B9F6C2039F3}" name="Parameter" dataDxfId="139"/>
+    <tableColumn id="1" xr3:uid="{BF4A73EA-A313-4283-BE5C-5B9F6C2039F3}" name="Parameter" dataDxfId="143"/>
     <tableColumn id="2" xr3:uid="{2168A1D6-1F00-420A-AE49-628879EF67CF}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{EE2AD78A-DCFF-47D8-A4FD-47301D7A564F}" name="Units" dataDxfId="138"/>
-    <tableColumn id="4" xr3:uid="{F7910500-F089-4E59-9AC8-5734EF06B071}" name="Source / note" dataDxfId="137"/>
+    <tableColumn id="3" xr3:uid="{EE2AD78A-DCFF-47D8-A4FD-47301D7A564F}" name="Units" dataDxfId="142"/>
+    <tableColumn id="4" xr3:uid="{F7910500-F089-4E59-9AC8-5734EF06B071}" name="Source / note" dataDxfId="141"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}" name="household_spend" displayName="household_spend" ref="A1:E11" totalsRowShown="0" headerRowDxfId="56" dataDxfId="54" headerRowBorderDxfId="55" tableBorderDxfId="53" totalsRowBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}" name="household_spend" displayName="household_spend" ref="A1:E11" totalsRowShown="0" headerRowDxfId="60" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57" totalsRowBorderDxfId="56">
   <autoFilter ref="A1:E11" xr:uid="{14481E30-4492-4DED-8E9A-2EC2D68F1FBA}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9A4690EE-FA56-405E-A30D-875570657134}" name="Typology / tenure" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{E91F277E-06CE-4EDB-8543-29E44E82DEA7}" name="Upper" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{1EAAF470-471D-4B0C-A575-DFBD58AEA1B8}" name="Central" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{57C7CBC2-465E-4D9C-862C-8B255FF6A5B2}" name="Lower" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{2AC2BF98-5348-4DE0-93F2-91C9D65F223E}" name="Units" dataDxfId="47"/>
+    <tableColumn id="1" xr3:uid="{9A4690EE-FA56-405E-A30D-875570657134}" name="Typology / tenure" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{E91F277E-06CE-4EDB-8543-29E44E82DEA7}" name="Upper" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{1EAAF470-471D-4B0C-A575-DFBD58AEA1B8}" name="Central" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{57C7CBC2-465E-4D9C-862C-8B255FF6A5B2}" name="Lower" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{2AC2BF98-5348-4DE0-93F2-91C9D65F223E}" name="Units" dataDxfId="51"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}" name="additionality_mappings" displayName="additionality_mappings" ref="A1:F16" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}" name="additionality_mappings" displayName="additionality_mappings" ref="A1:F16" totalsRowShown="0" headerRowDxfId="50" dataDxfId="48" headerRowBorderDxfId="49" tableBorderDxfId="47" totalsRowBorderDxfId="46">
   <autoFilter ref="A1:F16" xr:uid="{10CAE23F-64C2-446D-8AC7-2420C696FBA2}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{E3A723FA-457B-4EFE-9E92-EB013E337B59}" name="Group" dataDxfId="41"/>
-    <tableColumn id="2" xr3:uid="{02D51F27-6686-45C8-B830-EE4683B203DE}" name="Scenario" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{141761B2-F5F5-4B9A-8B3E-DC8AC7A74CBC}" name="Deadweight" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{73079F49-39D1-41A2-AF81-9562C0ADE495}" name="Displacement" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{BF1D37EB-AE48-4C08-9998-896BCDE53C45}" name="Leakage" dataDxfId="37"/>
-    <tableColumn id="6" xr3:uid="{343EC36C-1426-4634-AD97-7726BDCCA977}" name="Multiplier" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{E3A723FA-457B-4EFE-9E92-EB013E337B59}" name="Group" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{02D51F27-6686-45C8-B830-EE4683B203DE}" name="Scenario" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{141761B2-F5F5-4B9A-8B3E-DC8AC7A74CBC}" name="Deadweight" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{73079F49-39D1-41A2-AF81-9562C0ADE495}" name="Displacement" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{BF1D37EB-AE48-4C08-9998-896BCDE53C45}" name="Leakage" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{343EC36C-1426-4634-AD97-7726BDCCA977}" name="Multiplier" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{B1ED9103-DDDE-47B1-8810-5356D0BC801A}" name="discounting" displayName="discounting" ref="A1:D3" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33" totalsRowBorderDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{B1ED9103-DDDE-47B1-8810-5356D0BC801A}" name="discounting" displayName="discounting" ref="A1:D3" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37" totalsRowBorderDxfId="36">
   <autoFilter ref="A1:D3" xr:uid="{B1ED9103-DDDE-47B1-8810-5356D0BC801A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C9D1B6E6-554B-4728-999B-F79940D1548F}" name="Parameter" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{9CC8EED5-22B9-4B6C-ABA0-C94CA361A8EB}" name="Value" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{DF9EDA1C-294C-452B-BFF2-26FBD630BCD3}" name="Unit" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{D5D8E8F0-51CC-4FDB-ABC4-1CE5C67CF3DC}" name="Source" dataDxfId="28"/>
+    <tableColumn id="1" xr3:uid="{C9D1B6E6-554B-4728-999B-F79940D1548F}" name="Parameter" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{9CC8EED5-22B9-4B6C-ABA0-C94CA361A8EB}" name="Value" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{DF9EDA1C-294C-452B-BFF2-26FBD630BCD3}" name="Unit" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{D5D8E8F0-51CC-4FDB-ABC4-1CE5C67CF3DC}" name="Source" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{6423D1D0-30EB-48F7-8293-4EDC0FFE06C1}" name="discounting_by_impact" displayName="discounting_by_impact" ref="A1:D4" totalsRowShown="0" headerRowDxfId="27" headerRowBorderDxfId="26" tableBorderDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{6423D1D0-30EB-48F7-8293-4EDC0FFE06C1}" name="discounting_by_impact" displayName="discounting_by_impact" ref="A1:D4" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29">
   <autoFilter ref="A1:D4" xr:uid="{6423D1D0-30EB-48F7-8293-4EDC0FFE06C1}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BAA839D6-42E3-4FD9-8386-2108D73EF939}" name="Impact" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{BAA839D6-42E3-4FD9-8386-2108D73EF939}" name="Impact" dataDxfId="28"/>
     <tableColumn id="2" xr3:uid="{34EDF934-C8FE-4FFD-9217-6E193C221B78}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{6516570E-DCB9-4F5C-8D62-991AA6C746A7}" name="Unit" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{B4F1FF20-BFB8-46B8-A719-D89B829DB05B}" name="Notes" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{6516570E-DCB9-4F5C-8D62-991AA6C746A7}" name="Unit" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{B4F1FF20-BFB8-46B8-A719-D89B829DB05B}" name="Notes" dataDxfId="26"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}" name="land_infra_mult" displayName="land_infra_mult" ref="A1:D9" totalsRowShown="0" headerRowDxfId="150" headerRowBorderDxfId="149" tableBorderDxfId="148" totalsRowBorderDxfId="147">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}" name="land_infra_mult" displayName="land_infra_mult" ref="A1:D9" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <autoFilter ref="A1:D9" xr:uid="{4EB637CF-069E-41D0-AB72-259C07748F40}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{7FD0A6E6-1B0A-4FC7-81EC-4DD560B478DC}" name="Parameter" dataDxfId="146"/>
+    <tableColumn id="1" xr3:uid="{7FD0A6E6-1B0A-4FC7-81EC-4DD560B478DC}" name="Parameter" dataDxfId="21"/>
     <tableColumn id="2" xr3:uid="{A7B1CC4E-78DF-4D14-A750-3E88F52FAF2A}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{2E3AE3B4-C3F9-4F53-873A-03E831ED79B8}" name="Unit" dataDxfId="145"/>
-    <tableColumn id="4" xr3:uid="{4BF2B9CD-2B84-4D85-BBB6-91888AED0426}" name="Notes" dataDxfId="144"/>
+    <tableColumn id="3" xr3:uid="{2E3AE3B4-C3F9-4F53-873A-03E831ED79B8}" name="Unit" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{4BF2B9CD-2B84-4D85-BBB6-91888AED0426}" name="Notes" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9058E2D3-F7F9-4A10-BAB9-8320F53C6B23}" name="civic_eng_belong" displayName="civic_eng_belong" ref="A1:D4" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{9058E2D3-F7F9-4A10-BAB9-8320F53C6B23}" name="civic_eng_belong" displayName="civic_eng_belong" ref="A1:D4" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="A1:D4" xr:uid="{9058E2D3-F7F9-4A10-BAB9-8320F53C6B23}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{D75EF333-231B-4EAB-8E7D-12FB18EC5B22}" name="Parameter" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{D75EF333-231B-4EAB-8E7D-12FB18EC5B22}" name="Parameter" dataDxfId="14"/>
     <tableColumn id="2" xr3:uid="{8D56F066-D35D-4A74-A55B-3DD8CBAC3EC7}" name="Value"/>
-    <tableColumn id="3" xr3:uid="{F42C9F6C-C12D-472E-A3D9-29026D896399}" name="Unit" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{394C7EEE-A3A1-4B69-9201-FD078CF98397}" name="Notes" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{F42C9F6C-C12D-472E-A3D9-29026D896399}" name="Unit" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{394C7EEE-A3A1-4B69-9201-FD078CF98397}" name="Notes" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{2F61142E-C399-4A09-80C9-11F84EFA0201}" name="commercial_floorspace" displayName="commercial_floorspace" ref="A1:D6" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" totalsRowBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{2F61142E-C399-4A09-80C9-11F84EFA0201}" name="commercial_floorspace" displayName="commercial_floorspace" ref="A1:D6" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="A1:D6" xr:uid="{2F61142E-C399-4A09-80C9-11F84EFA0201}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{32EDEB91-4F8A-4846-9FCB-55E9F2D4B2E6}" name="Category" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{84D454D1-33DD-4384-B598-B4192219381D}" name="Floorspace density" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{EBC3F3AB-86F1-45B4-A769-0AED9DFD997D}" name="Avg GVA per FTE job" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{4CB0938F-48BB-4717-B1A0-24CD58794538}" name="Note" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{32EDEB91-4F8A-4846-9FCB-55E9F2D4B2E6}" name="Category" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{84D454D1-33DD-4384-B598-B4192219381D}" name="Floorspace density" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{EBC3F3AB-86F1-45B4-A769-0AED9DFD997D}" name="Avg GVA per FTE job" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{4CB0938F-48BB-4717-B1A0-24CD58794538}" name="Note" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{A0AD5514-D5BE-4C31-8C6F-0CDAB9F32808}" name="discounting_control" displayName="discounting_control" ref="A1:B5" totalsRowShown="0" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{A0AD5514-D5BE-4C31-8C6F-0CDAB9F32808}" name="discounting_control" displayName="discounting_control" ref="A1:B5" totalsRowShown="0" headerRowBorderDxfId="3" tableBorderDxfId="2" totalsRowBorderDxfId="1">
   <autoFilter ref="A1:B5" xr:uid="{A0AD5514-D5BE-4C31-8C6F-0CDAB9F32808}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{3751DEC9-2A4C-4639-A38F-290EEE1255EA}" name="Parameter" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{3751DEC9-2A4C-4639-A38F-290EEE1255EA}" name="Parameter" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{F05864C2-7639-4B7E-8486-057A8978B244}" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5289,129 +5289,129 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{70FD85FB-2C29-4261-8C5D-B4A82FB6DD29}" name="land_value_controls" displayName="land_value_controls" ref="A1:B4" totalsRowShown="0" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="18" xr:uid="{70FD85FB-2C29-4261-8C5D-B4A82FB6DD29}" name="land_value_controls" displayName="land_value_controls" ref="A1:B4" totalsRowShown="0" tableBorderDxfId="150">
   <autoFilter ref="A1:B4" xr:uid="{70FD85FB-2C29-4261-8C5D-B4A82FB6DD29}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{A262D807-2770-47C5-A118-D0BEE2C6E0FF}" name="Parameter" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{8A0060A0-6DE4-41F5-84C9-693FAB036024}" name="Value" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{A262D807-2770-47C5-A118-D0BEE2C6E0FF}" name="Parameter" dataDxfId="149"/>
+    <tableColumn id="2" xr3:uid="{8A0060A0-6DE4-41F5-84C9-693FAB036024}" name="Value" dataDxfId="148"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}" name="dwellingbytypology" displayName="dwellingbytypology" ref="A1:H6" totalsRowShown="0" headerRowDxfId="136" dataDxfId="134" headerRowBorderDxfId="135" tableBorderDxfId="133" totalsRowBorderDxfId="132">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}" name="dwellingbytypology" displayName="dwellingbytypology" ref="A1:H6" totalsRowShown="0" headerRowDxfId="140" dataDxfId="138" headerRowBorderDxfId="139" tableBorderDxfId="137" totalsRowBorderDxfId="136">
   <autoFilter ref="A1:H6" xr:uid="{0E3C03BC-9795-4A32-BE15-F23695000642}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{AF5B1002-ACF0-443F-BA91-D855456C8E2D}" name="Typology" dataDxfId="131"/>
-    <tableColumn id="2" xr3:uid="{4552E384-A064-4D7E-B638-6DC25252B385}" name="Floorspace m2" dataDxfId="130"/>
-    <tableColumn id="3" xr3:uid="{E22864B2-160F-4F3D-9491-0A60A9310C41}" name="Persons Per Dwelling - Private" dataDxfId="129"/>
-    <tableColumn id="4" xr3:uid="{0377E05F-6D73-4E82-AD3D-2AA209958578}" name="Persons Per Dwelling - Social/affordable" dataDxfId="128"/>
-    <tableColumn id="5" xr3:uid="{3D93BA7B-360E-4A20-BB94-AFEC8DAB2F05}" name="Council Tax per unit" dataDxfId="127"/>
-    <tableColumn id="6" xr3:uid="{E1042461-7B4B-4E4A-96C1-EA75409C533A}" name="Rent per social/MMR unit" dataDxfId="126"/>
-    <tableColumn id="7" xr3:uid="{56B6CFB9-570D-4CC0-9162-B0D0FCE94F69}" name="Private disposable income" dataDxfId="125"/>
-    <tableColumn id="8" xr3:uid="{CA5B102B-23EE-4F5D-853D-87DFD7D74ACA}" name="Social/affordable disposable income" dataDxfId="124"/>
+    <tableColumn id="1" xr3:uid="{AF5B1002-ACF0-443F-BA91-D855456C8E2D}" name="Typology" dataDxfId="135"/>
+    <tableColumn id="2" xr3:uid="{4552E384-A064-4D7E-B638-6DC25252B385}" name="Floorspace m2" dataDxfId="134"/>
+    <tableColumn id="3" xr3:uid="{E22864B2-160F-4F3D-9491-0A60A9310C41}" name="Persons Per Dwelling - Private" dataDxfId="133"/>
+    <tableColumn id="4" xr3:uid="{0377E05F-6D73-4E82-AD3D-2AA209958578}" name="Persons Per Dwelling - Social/affordable" dataDxfId="132"/>
+    <tableColumn id="5" xr3:uid="{3D93BA7B-360E-4A20-BB94-AFEC8DAB2F05}" name="Council Tax per unit" dataDxfId="131"/>
+    <tableColumn id="6" xr3:uid="{E1042461-7B4B-4E4A-96C1-EA75409C533A}" name="Rent per social/MMR unit" dataDxfId="130"/>
+    <tableColumn id="7" xr3:uid="{56B6CFB9-570D-4CC0-9162-B0D0FCE94F69}" name="Private disposable income" dataDxfId="129"/>
+    <tableColumn id="8" xr3:uid="{CA5B102B-23EE-4F5D-853D-87DFD7D74ACA}" name="Social/affordable disposable income" dataDxfId="128"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}" name="pop_employ" displayName="pop_employ" ref="A1:E6" totalsRowShown="0" headerRowDxfId="123" headerRowBorderDxfId="122" tableBorderDxfId="121" totalsRowBorderDxfId="120">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}" name="pop_employ" displayName="pop_employ" ref="A1:E6" totalsRowShown="0" headerRowDxfId="127" headerRowBorderDxfId="126" tableBorderDxfId="125" totalsRowBorderDxfId="124">
   <autoFilter ref="A1:E6" xr:uid="{5D2D2174-90B9-463F-9330-0CCD3522FDE1}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{947CE13C-D8BA-437F-95E3-C118D991F51E}" name="Parameter" dataDxfId="119"/>
-    <tableColumn id="2" xr3:uid="{07D50781-49CC-4BF6-8A8F-30D3D0C13A42}" name="Private" dataDxfId="118"/>
-    <tableColumn id="3" xr3:uid="{9642AD60-1B5A-4683-8E0B-12D1FE0BEBCA}" name="Social/affordable" dataDxfId="117"/>
-    <tableColumn id="5" xr3:uid="{E72D4F67-11C4-42E3-B5A3-627689ABEEC2}" name="Older person" dataDxfId="116"/>
-    <tableColumn id="4" xr3:uid="{D8D5E346-3E52-4B56-B72E-C2C8E3B487BA}" name="Units" dataDxfId="115"/>
+    <tableColumn id="1" xr3:uid="{947CE13C-D8BA-437F-95E3-C118D991F51E}" name="Parameter" dataDxfId="123"/>
+    <tableColumn id="2" xr3:uid="{07D50781-49CC-4BF6-8A8F-30D3D0C13A42}" name="Private" dataDxfId="122"/>
+    <tableColumn id="3" xr3:uid="{9642AD60-1B5A-4683-8E0B-12D1FE0BEBCA}" name="Social/affordable" dataDxfId="121"/>
+    <tableColumn id="5" xr3:uid="{E72D4F67-11C4-42E3-B5A3-627689ABEEC2}" name="Older person" dataDxfId="120"/>
+    <tableColumn id="4" xr3:uid="{D8D5E346-3E52-4B56-B72E-C2C8E3B487BA}" name="Units" dataDxfId="119"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}" name="transport_modal" displayName="transport_modal" ref="A1:H9" totalsRowShown="0" headerRowDxfId="114" dataDxfId="112" headerRowBorderDxfId="113" tableBorderDxfId="111" totalsRowBorderDxfId="110">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}" name="transport_modal" displayName="transport_modal" ref="A1:H9" totalsRowShown="0" headerRowDxfId="118" dataDxfId="116" headerRowBorderDxfId="117" tableBorderDxfId="115" totalsRowBorderDxfId="114">
   <autoFilter ref="A1:H9" xr:uid="{79CADA8C-6739-4499-8318-8C1A1D43CE67}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{51D80002-D764-4804-8EC7-BF057B59E144}" name="Mode" dataDxfId="109"/>
-    <tableColumn id="2" xr3:uid="{632F4F89-D565-43F4-8508-41B297AC72E4}" name="Baseline share" dataDxfId="108"/>
-    <tableColumn id="3" xr3:uid="{F88145F9-8928-434C-8CDB-20D90AA0024C}" name="TCL Good" dataDxfId="107"/>
-    <tableColumn id="4" xr3:uid="{B0EC6125-F09D-4332-8FAF-A316F08C437C}" name="TCL Average" dataDxfId="106"/>
-    <tableColumn id="5" xr3:uid="{5AF3B7FB-6119-4BB3-BE48-1C87DAEBA045}" name="TCL Limited" dataDxfId="105"/>
-    <tableColumn id="6" xr3:uid="{28476781-DBA7-44F7-8DFF-F6C7E20BF879}" name="Baseline km" dataDxfId="104"/>
-    <tableColumn id="7" xr3:uid="{15EB3372-9D4F-46B3-A45C-B008382479FA}" name="Emission factor kgCO2e/pkm" dataDxfId="103"/>
-    <tableColumn id="8" xr3:uid="{7C2A1136-FFE8-4A44-AC30-D20CEB0F77DF}" name="Speed km/h" dataDxfId="102"/>
+    <tableColumn id="1" xr3:uid="{51D80002-D764-4804-8EC7-BF057B59E144}" name="Mode" dataDxfId="113"/>
+    <tableColumn id="2" xr3:uid="{632F4F89-D565-43F4-8508-41B297AC72E4}" name="Baseline share" dataDxfId="112"/>
+    <tableColumn id="3" xr3:uid="{F88145F9-8928-434C-8CDB-20D90AA0024C}" name="TCL Good" dataDxfId="111"/>
+    <tableColumn id="4" xr3:uid="{B0EC6125-F09D-4332-8FAF-A316F08C437C}" name="TCL Average" dataDxfId="110"/>
+    <tableColumn id="5" xr3:uid="{5AF3B7FB-6119-4BB3-BE48-1C87DAEBA045}" name="TCL Limited" dataDxfId="109"/>
+    <tableColumn id="6" xr3:uid="{28476781-DBA7-44F7-8DFF-F6C7E20BF879}" name="Baseline km" dataDxfId="108"/>
+    <tableColumn id="7" xr3:uid="{15EB3372-9D4F-46B3-A45C-B008382479FA}" name="Emission factor kgCO2e/pkm" dataDxfId="107"/>
+    <tableColumn id="8" xr3:uid="{7C2A1136-FFE8-4A44-AC30-D20CEB0F77DF}" name="Speed km/h" dataDxfId="106"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}" name="carbon" displayName="carbon" ref="A1:F4" totalsRowShown="0" headerRowDxfId="101" dataDxfId="99" headerRowBorderDxfId="100" tableBorderDxfId="98" totalsRowBorderDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}" name="carbon" displayName="carbon" ref="A1:F4" totalsRowShown="0" headerRowDxfId="105" dataDxfId="103" headerRowBorderDxfId="104" tableBorderDxfId="102" totalsRowBorderDxfId="101">
   <autoFilter ref="A1:F4" xr:uid="{B5EB96F9-732E-4614-BCD1-33C1639E5F61}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{80B2580A-D788-4184-8B9B-91481871C1B1}" name="Development type" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{E2B4663C-5E14-40B1-B0E0-9F536D5994B1}" name="Low upfront" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{4F8B9403-C34D-4A52-AFD9-86BB230C316D}" name="Medium upfront" dataDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{148042E5-61B0-4045-9632-78DA909DE42D}" name="High upfront" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{8A4AFD31-51B7-45FE-8D58-B6C8F3E1E731}" name="Baseline comparator" dataDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{C11B7004-AD50-4B91-A6AC-2CD2E104AC48}" name="End of life factor" dataDxfId="91"/>
+    <tableColumn id="1" xr3:uid="{80B2580A-D788-4184-8B9B-91481871C1B1}" name="Development type" dataDxfId="100"/>
+    <tableColumn id="2" xr3:uid="{E2B4663C-5E14-40B1-B0E0-9F536D5994B1}" name="Low upfront" dataDxfId="99"/>
+    <tableColumn id="3" xr3:uid="{4F8B9403-C34D-4A52-AFD9-86BB230C316D}" name="Medium upfront" dataDxfId="98"/>
+    <tableColumn id="4" xr3:uid="{148042E5-61B0-4045-9632-78DA909DE42D}" name="High upfront" dataDxfId="97"/>
+    <tableColumn id="5" xr3:uid="{8A4AFD31-51B7-45FE-8D58-B6C8F3E1E731}" name="Baseline comparator" dataDxfId="96"/>
+    <tableColumn id="6" xr3:uid="{C11B7004-AD50-4B91-A6AC-2CD2E104AC48}" name="End of life factor" dataDxfId="95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}" name="environ_wellbeingTable6" displayName="environ_wellbeingTable6" ref="A1:E6" totalsRowShown="0" headerRowDxfId="90" headerRowBorderDxfId="89" tableBorderDxfId="88" totalsRowBorderDxfId="87">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}" name="environ_wellbeingTable6" displayName="environ_wellbeingTable6" ref="A1:E6" totalsRowShown="0" headerRowDxfId="94" headerRowBorderDxfId="93" tableBorderDxfId="92" totalsRowBorderDxfId="91">
   <autoFilter ref="A1:E6" xr:uid="{AC749976-DD17-482A-9FD7-9196F207272A}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{04476D43-8F73-422A-9656-FA2B9CD22585}" name="Parameter" dataDxfId="86"/>
-    <tableColumn id="2" xr3:uid="{76480CDF-9E60-4089-A0A3-B5493DDC105F}" name="Lower scale impact" dataDxfId="85"/>
+    <tableColumn id="1" xr3:uid="{04476D43-8F73-422A-9656-FA2B9CD22585}" name="Parameter" dataDxfId="90"/>
+    <tableColumn id="2" xr3:uid="{76480CDF-9E60-4089-A0A3-B5493DDC105F}" name="Lower scale impact" dataDxfId="89"/>
     <tableColumn id="3" xr3:uid="{AB078BD6-DFAE-44D5-A871-78C491E01176}" name="Central impact"/>
     <tableColumn id="4" xr3:uid="{75FA526C-FBEE-4599-B606-702D6554E485}" name="Higher scale impact"/>
-    <tableColumn id="5" xr3:uid="{0BDF18F5-C495-4B11-AD1B-3043B7B15F46}" name="Units" dataDxfId="84"/>
+    <tableColumn id="5" xr3:uid="{0BDF18F5-C495-4B11-AD1B-3043B7B15F46}" name="Units" dataDxfId="88"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}" name="active_travel" displayName="active_travel" ref="A1:G4" totalsRowShown="0" headerRowDxfId="83" dataDxfId="81" headerRowBorderDxfId="82" tableBorderDxfId="80" totalsRowBorderDxfId="79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}" name="active_travel" displayName="active_travel" ref="A1:G4" totalsRowShown="0" headerRowDxfId="87" dataDxfId="85" headerRowBorderDxfId="86" tableBorderDxfId="84" totalsRowBorderDxfId="83">
   <autoFilter ref="A1:G4" xr:uid="{DC131DAF-A5A6-4609-9BBD-D774FD2E423D}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{AD78C056-5CC9-4CD9-B25A-9E1FDA7619ED}" name="Accessibility" dataDxfId="78"/>
-    <tableColumn id="2" xr3:uid="{DDB6924C-0BED-4161-92F2-8EF3A236C4E5}" name="Walking uplift" dataDxfId="77"/>
-    <tableColumn id="3" xr3:uid="{9C68EE70-0111-4A45-8C9E-3C0000BE8EB3}" name="Cycling uplift" dataDxfId="76"/>
-    <tableColumn id="4" xr3:uid="{727BFA19-FC13-457E-A671-2032BFC507A9}" name="Minutes uplift" dataDxfId="75"/>
-    <tableColumn id="5" xr3:uid="{4EF746B4-929E-4ADE-9844-064C65AA8AF6}" name="Baseline meeting 150 mins (high deprivation)" dataDxfId="74"/>
-    <tableColumn id="6" xr3:uid="{A508C7D2-8286-46AA-AE93-0CFD202BABC6}" name="Baseline meeting 150 mins (average deprivation)" dataDxfId="73"/>
-    <tableColumn id="7" xr3:uid="{DA5F9070-A695-4818-AAC9-61F124AC7F92}" name="Baseline meeting 150 mins (low deprivation)" dataDxfId="72"/>
+    <tableColumn id="1" xr3:uid="{AD78C056-5CC9-4CD9-B25A-9E1FDA7619ED}" name="Accessibility" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{DDB6924C-0BED-4161-92F2-8EF3A236C4E5}" name="Walking uplift" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{9C68EE70-0111-4A45-8C9E-3C0000BE8EB3}" name="Cycling uplift" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{727BFA19-FC13-457E-A671-2032BFC507A9}" name="Minutes uplift" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{4EF746B4-929E-4ADE-9844-064C65AA8AF6}" name="Baseline meeting 150 mins (high deprivation)" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{A508C7D2-8286-46AA-AE93-0CFD202BABC6}" name="Baseline meeting 150 mins (average deprivation)" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{DA5F9070-A695-4818-AAC9-61F124AC7F92}" name="Baseline meeting 150 mins (low deprivation)" dataDxfId="76"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}" name="crime" displayName="crime" ref="A1:D5" totalsRowShown="0" headerRowDxfId="71" headerRowBorderDxfId="70" tableBorderDxfId="69" totalsRowBorderDxfId="68">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}" name="crime" displayName="crime" ref="A1:D5" totalsRowShown="0" headerRowDxfId="75" headerRowBorderDxfId="74" tableBorderDxfId="73" totalsRowBorderDxfId="72">
   <autoFilter ref="A1:D5" xr:uid="{EF810BE9-7C6F-4265-8DEC-A1CDB6675747}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{907E3F67-1965-41D5-8DDD-707389C0597D}" name="Category" dataDxfId="67"/>
-    <tableColumn id="2" xr3:uid="{02A1EC8D-CE03-4112-AF55-3E5058D292AE}" name="Rate per 1,000" dataDxfId="66"/>
-    <tableColumn id="3" xr3:uid="{C292AD1E-37A6-4421-A549-FB7A56194F0B}" name="Cost per incident" dataDxfId="65"/>
-    <tableColumn id="4" xr3:uid="{7F206B66-30F3-4010-AC15-A9AFDE66E061}" name="Reduction rate" dataDxfId="64"/>
+    <tableColumn id="1" xr3:uid="{907E3F67-1965-41D5-8DDD-707389C0597D}" name="Category" dataDxfId="71"/>
+    <tableColumn id="2" xr3:uid="{02A1EC8D-CE03-4112-AF55-3E5058D292AE}" name="Rate per 1,000" dataDxfId="70"/>
+    <tableColumn id="3" xr3:uid="{C292AD1E-37A6-4421-A549-FB7A56194F0B}" name="Cost per incident" dataDxfId="69"/>
+    <tableColumn id="4" xr3:uid="{7F206B66-30F3-4010-AC15-A9AFDE66E061}" name="Reduction rate" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}" name="economic_coeff" displayName="economic_coeff" ref="A1:C8" totalsRowShown="0" headerRowDxfId="63" headerRowBorderDxfId="62" tableBorderDxfId="61" totalsRowBorderDxfId="60">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}" name="economic_coeff" displayName="economic_coeff" ref="A1:C8" totalsRowShown="0" headerRowDxfId="67" headerRowBorderDxfId="66" tableBorderDxfId="65" totalsRowBorderDxfId="64">
   <autoFilter ref="A1:C8" xr:uid="{55D7EC45-CE5C-44FC-B5E0-0BAFE887560C}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B3E4FC91-3B70-4B5F-BE4B-3D95311501D9}" name="Parameter" dataDxfId="59"/>
-    <tableColumn id="2" xr3:uid="{8E11059B-045B-4658-BEA4-ACFA568B296F}" name="Value" dataDxfId="58"/>
-    <tableColumn id="3" xr3:uid="{97CBA549-19DB-408B-AA6F-BDFA09076EB0}" name="Units" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{B3E4FC91-3B70-4B5F-BE4B-3D95311501D9}" name="Parameter" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{8E11059B-045B-4658-BEA4-ACFA568B296F}" name="Value" dataDxfId="62"/>
+    <tableColumn id="3" xr3:uid="{97CBA549-19DB-408B-AA6F-BDFA09076EB0}" name="Units" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6603,7 +6603,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
         <v>150</v>
       </c>
@@ -7700,7 +7700,7 @@
         <v>74</v>
       </c>
       <c r="B6" s="25">
-        <v>2.5000000000000001E-2</v>
+        <v>0.01</v>
       </c>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
@@ -7995,7 +7995,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>100</v>
       </c>
@@ -8006,7 +8006,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>101</v>
       </c>
